--- a/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_645_Russia_Barents_Sea.xlsx
+++ b/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_645_Russia_Barents_Sea.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="R6adb345fdb5745ef"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="R954323ee8d2346dc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="R0034cd43985d42e6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="Rfcd3122481544ee1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="R3e0281da71cb4299"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="R38585a05fefd49f7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="Rebfc1a6f66394249"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="Rb06f87a2d1724f1f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="Ra8878d68ccea4eb4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="R1b5157263f42454d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="R6a0be637477c45f4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="R12c284ffd9094b86"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -18,13 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="6">
+  <x:numFmts count="4">
     <x:numFmt numFmtId="200" formatCode="0"/>
     <x:numFmt numFmtId="201" formatCode="#,##0.00"/>
     <x:numFmt numFmtId="202" formatCode="0.0000"/>
-    <x:numFmt numFmtId="203" formatCode="#,##0"/>
-    <x:numFmt numFmtId="204" formatCode="0.00%"/>
-    <x:numFmt numFmtId="205" formatCode="0.00"/>
+    <x:numFmt numFmtId="203" formatCode="0.00"/>
   </x:numFmts>
   <x:fonts count="7">
     <x:font>
@@ -184,7 +182,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="37">
+  <x:cellXfs count="35">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <x:extLst>
@@ -244,8 +242,6 @@
     <x:xf numFmtId="200" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="201" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="202" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="203" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="204" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <x:extLst>
         <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
@@ -253,14 +249,14 @@
         </x:ext>
       </x:extLst>
     </x:xf>
-    <x:xf numFmtId="205" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="203" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
-  <x:dxfs count="3">
+  <x:dxfs count="1">
     <x:dxf>
       <x:font>
         <x:color rgb="FF9A3412"/>
@@ -268,28 +264,6 @@
       <x:fill>
         <x:patternFill patternType="solid">
           <x:bgColor rgb="FFFCEAD8"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
         </x:patternFill>
       </x:fill>
     </x:dxf>
@@ -345,56 +319,36 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ645CommercialTable" displayName="EEZ645CommercialTable" ref="A1:O11" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O11"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ645CommercialTable" displayName="EEZ645CommercialTable" ref="A1:E11" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E11"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="commercial_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ645FunctionalTable" displayName="EEZ645FunctionalTable" ref="A1:O18" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O18"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ645FunctionalTable" displayName="EEZ645FunctionalTable" ref="A1:E18" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E18"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="functional_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ645ValidationTable" displayName="EEZ645ValidationTable" ref="A1:D19" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:D19"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ645ValidationTable" displayName="EEZ645ValidationTable" ref="A1:D17" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:D17"/>
   <x:tableColumns count="4">
     <x:tableColumn id="1" name="unit_id"/>
     <x:tableColumn id="2" name="check"/>
@@ -6456,7 +6410,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R634eddaff3a843ec"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Raccd9932a90b413d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6466,20 +6420,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="26" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -6487,606 +6431,212 @@
         <x:v>commercial_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Cod-likes</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>190832.3330938893</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>4.075254415014003</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>1189.1986705362974</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>190832.3330938893</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>1206.4277186770348</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$H$2:$H$87,A2,'Species'!$U$2:$U$87))</x:f>
-        <x:v>230225416.2642769</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>4.075254415014003</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>1189.1986705362974</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>226937556.810593</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>3287859.453683883</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1.01448794769756</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0.014487947697559825</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Crustaceans</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>16098.0022037795</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>3.6183264235981505</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>415.2660468474025</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>16098.0022037795</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>422.97336910878397</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$H$2:$H$87,A3,'Species'!$U$2:$U$87))</x:f>
-        <x:v>6809026.228053245</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>3.6183264235981505</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>415.2660468474025</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>6684953.737304287</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>124072.49074895773</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1.0185599625105244</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0.018559962510524428</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Flatfishes</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>13472.3691533404</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>3.53988181463753</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>346.6425051483892</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>13472.3691533404</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>628.9920122896621</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$H$2:$H$87,A4,'Species'!$U$2:$U$87))</x:f>
-        <x:v>8474012.58406875</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>3.53988181463753</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>346.6425051483892</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>4670095.7935978</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>3803916.7904709494</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1.8145265019372216</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0.8145265019372218</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Herring-likes</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>1068.491032814</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>3.3412152558678274</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>219.38920574393708</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>1068.491032814</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>223.0755149414232</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$H$2:$H$87,A5,'Species'!$U$2:$U$87))</x:f>
-        <x:v>238354.18735527614</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>3.3412152558678274</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>219.38920574393708</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>234415.39903358245</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>3938.78832169369</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>1.0168026005882378</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>0.01680260058823788</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Molluscs</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>12.0232923311</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>2.019537947107746</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>10.460150835493268</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>12.0232923311</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>11.201503566167187</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$H$2:$H$87,A6,'Species'!$U$2:$U$87))</x:f>
-        <x:v>134.67895192388724</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>2.019537947107746</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>10.460150835493268</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>125.76545132253547</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>8.913500601351771</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1.0708740000343369</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0.07087400003433687</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Other fishes &amp; inverts</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>24787.113693249205</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>3.27078723885127</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>186.54655741435033</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>24787.113693249205</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>188.6771813094793</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$H$2:$H$87,A7,'Species'!$U$2:$U$87))</x:f>
-        <x:v>4676762.744439857</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>3.27078723885127</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>186.54655741435033</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>4623950.727713742</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>52812.01672611479</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>1.0114214055979414</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>0.011421405597941366</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Perch-likes</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>7855.289832462699</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>3.578149923447253</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>378.57324999971615</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>7855.289832462699</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>404.8506234999867</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$H$2:$H$87,A8,'Species'!$U$2:$U$87))</x:f>
-        <x:v>3180218.98644563</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>3.578149923447253</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>378.57324999971615</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>2973802.60156513</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>206416.3848804999</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>1.069411596039314</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>0.06941159603931402</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="24" t="str">
         <x:v>Salmon, smelts, etc</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
+      <x:c r="B9" s="31" t="n">
         <x:v>372.7316754823999</x:v>
       </x:c>
+      <x:c r="C9" s="32" t="n">
+        <x:v>3.8659377500446714</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="n">
+        <x:f>IF(C9="","",(1/'Metadata'!$B$5)^(C9-1))</x:f>
+        <x:v>734.4085935551151</x:v>
+      </x:c>
       <x:c r="E9" s="31" t="n">
-        <x:v>372.7316754823999</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
-        <x:f>IF(E9=0,"",I9/E9)</x:f>
-        <x:v>1729.0031757277907</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="n">
-        <x:f>IF(C9=0,"",SUMIF('Species'!$H$2:$H$87,A9,'Species'!$U$2:$U$87))</x:f>
-        <x:v>644454.2506034097</x:v>
-      </x:c>
-      <x:c r="J9" s="32" t="n">
-        <x:v>3.8659377500446714</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>IF(J9="","",(1/'Metadata'!$B$5)^(J9-1))</x:f>
-        <x:v>734.4085935551151</x:v>
-      </x:c>
-      <x:c r="L9" s="31" t="n">
-        <x:f>IF(E9=0,"",E9*K9)</x:f>
+        <x:f>IF(B9=0,"",B9*D9)</x:f>
         <x:v>273737.3455644709</x:v>
-      </x:c>
-      <x:c r="M9" s="31" t="n">
-        <x:f>IF(E9=0,"",I9-L9)</x:f>
-        <x:v>370716.9050389388</x:v>
-      </x:c>
-      <x:c r="N9" s="32" t="n">
-        <x:f>IF(L9=0,"",I9/L9)</x:f>
-        <x:v>2.35427960797416</x:v>
-      </x:c>
-      <x:c r="O9" s="34" t="n">
-        <x:f>IF(L9=0,"",M9/L9)</x:f>
-        <x:v>1.35427960797416</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="18" customHeight="1">
       <x:c r="A10" s="24" t="str">
         <x:v>Scorpionfishes</x:v>
       </x:c>
-      <x:c r="B10" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C10" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D10" s="31" t="n">
+      <x:c r="B10" s="31" t="n">
         <x:v>2743.3086283727</x:v>
       </x:c>
+      <x:c r="C10" s="32" t="n">
+        <x:v>3.808645157524055</x:v>
+      </x:c>
+      <x:c r="D10" s="32" t="n">
+        <x:f>IF(C10="","",(1/'Metadata'!$B$5)^(C10-1))</x:f>
+        <x:v>643.643158757204</x:v>
+      </x:c>
       <x:c r="E10" s="31" t="n">
-        <x:v>2743.3086283727</x:v>
-      </x:c>
-      <x:c r="F10" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H10" s="32" t="n">
-        <x:f>IF(E10=0,"",I10/E10)</x:f>
-        <x:v>656.8398698947555</x:v>
-      </x:c>
-      <x:c r="I10" s="31" t="n">
-        <x:f>IF(C10=0,"",SUMIF('Species'!$H$2:$H$87,A10,'Species'!$U$2:$U$87))</x:f>
-        <x:v>1801914.4825414843</x:v>
-      </x:c>
-      <x:c r="J10" s="32" t="n">
-        <x:v>3.808645157524055</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:f>IF(J10="","",(1/'Metadata'!$B$5)^(J10-1))</x:f>
-        <x:v>643.643158757204</x:v>
-      </x:c>
-      <x:c r="L10" s="31" t="n">
-        <x:f>IF(E10=0,"",E10*K10)</x:f>
+        <x:f>IF(B10=0,"",B10*D10)</x:f>
         <x:v>1765711.8310116972</x:v>
-      </x:c>
-      <x:c r="M10" s="31" t="n">
-        <x:f>IF(E10=0,"",I10-L10)</x:f>
-        <x:v>36202.65152978711</x:v>
-      </x:c>
-      <x:c r="N10" s="32" t="n">
-        <x:f>IF(L10=0,"",I10/L10)</x:f>
-        <x:v>1.0205031483019764</x:v>
-      </x:c>
-      <x:c r="O10" s="34" t="n">
-        <x:f>IF(L10=0,"",M10/L10)</x:f>
-        <x:v>0.020503148301976394</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="18" customHeight="1">
       <x:c r="A11" s="24" t="str">
         <x:v>Sharks &amp; rays</x:v>
       </x:c>
-      <x:c r="B11" s="33" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="C11" s="33" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="D11" s="31" t="n">
+      <x:c r="B11" s="31" t="n">
         <x:v>396.84121454039996</x:v>
       </x:c>
+      <x:c r="C11" s="32" t="n">
+        <x:v>3.8044664697538937</x:v>
+      </x:c>
+      <x:c r="D11" s="32" t="n">
+        <x:f>IF(C11="","",(1/'Metadata'!$B$5)^(C11-1))</x:f>
+        <x:v>637.4798617086224</x:v>
+      </x:c>
       <x:c r="E11" s="31" t="n">
-        <x:v>396.84121454039996</x:v>
-      </x:c>
-      <x:c r="F11" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G11" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H11" s="32" t="n">
-        <x:f>IF(E11=0,"",I11/E11)</x:f>
-        <x:v>640.053270795148</x:v>
-      </x:c>
-      <x:c r="I11" s="31" t="n">
-        <x:f>IF(C11=0,"",SUMIF('Species'!$H$2:$H$87,A11,'Species'!$U$2:$U$87))</x:f>
-        <x:v>253999.51735290207</x:v>
-      </x:c>
-      <x:c r="J11" s="32" t="n">
-        <x:v>3.8044664697538937</x:v>
-      </x:c>
-      <x:c r="K11" s="32" t="n">
-        <x:f>IF(J11="","",(1/'Metadata'!$B$5)^(J11-1))</x:f>
-        <x:v>637.4798617086224</x:v>
-      </x:c>
-      <x:c r="L11" s="31" t="n">
-        <x:f>IF(E11=0,"",E11*K11)</x:f>
+        <x:f>IF(B11=0,"",B11*D11)</x:f>
         <x:v>252978.2825654959</x:v>
       </x:c>
-      <x:c r="M11" s="31" t="n">
-        <x:f>IF(E11=0,"",I11-L11)</x:f>
-        <x:v>1021.234787406167</x:v>
-      </x:c>
-      <x:c r="N11" s="32" t="n">
-        <x:f>IF(L11=0,"",I11/L11)</x:f>
-        <x:v>1.0040368476576316</x:v>
-      </x:c>
-      <x:c r="O11" s="34" t="n">
-        <x:f>IF(L11=0,"",M11/L11)</x:f>
-        <x:v>0.00403684765763152</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G11">
-    <x:cfRule type="cellIs" dxfId="1" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O11">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdcf25ebe53494ca5"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R36aad0e125954a4e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7096,20 +6646,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="34" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -7117,984 +6657,345 @@
         <x:v>functional_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Large benthopelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>140967.1105537891</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>4.083873004106363</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>1213.0340845634748</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>140967.1105537891</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>1222.3699097941471</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$G$2:$G$87,A2,'Species'!$U$2:$U$87))</x:f>
-        <x:v>172313954.21157676</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>4.083873004106363</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>1213.0340845634748</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>170997909.9041737</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>1316044.3074030578</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1.007696259610077</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0.007696259610076883</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Large demersals (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>8223.528102038</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>3.8484840473627955</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>705.4789297077592</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>8223.528102038</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>1101.174351018855</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$G$2:$G$87,A3,'Species'!$U$2:$U$87))</x:f>
-        <x:v>9055538.220847012</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>3.8484840473627955</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>705.4789297077592</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>5801525.803847449</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>3254012.4169995636</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1.560889070740937</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0.5608890707409371</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Large flatfishes (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>8202.3332642106</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>3.26</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>181.97008586099827</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>8202.3332642106</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>181.97008586099827</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$G$2:$G$87,A4,'Species'!$U$2:$U$87))</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>1492579.288348925</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>3.26</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>181.97008586099827</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
-        <x:v>1492579.288348925</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Large rays (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>4.3669975112</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>3.8151621606836694</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>653.3744697981892</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>4.3669975112</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>661.869306193202</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$G$2:$G$87,A5,'Species'!$U$2:$U$87))</x:f>
-        <x:v>2890.3816128853837</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>3.8151621606836694</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>653.3744697981892</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>2853.284683490312</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>37.096929395071584</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>1.0130014819796012</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>0.013001481979601262</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Large reef assoc. fish (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>2332.6316756609</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>3.7843701057964867</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>608.6534748716739</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>2332.6316756609</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>612.5566286871883</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$G$2:$G$87,A6,'Species'!$U$2:$U$87))</x:f>
-        <x:v>1428868.9952117878</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>3.7843701057964867</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>608.6534748716739</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>1419764.3749867422</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>9104.620225045597</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1.0064127684744384</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0.006412768474438314</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Large sharks (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>7.2230177544</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>4.0362262176129375</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>1086.991674168469</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>7.2230177544</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>1112.0091852032897</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$G$2:$G$87,A7,'Species'!$U$2:$U$87))</x:f>
-        <x:v>8032.062087779239</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>4.0362262176129375</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>1086.991674168469</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>7851.360161403832</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>180.7019263754073</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>1.0230153658296957</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>0.02301536582969563</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Lobsters, crabs</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>16097.876687515101</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>3.6183328307050564</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>415.2721732747317</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>16097.876687515101</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>422.976112726413</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$G$2:$G$87,A8,'Species'!$U$2:$U$87))</x:f>
-        <x:v>6809017.304434284</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>3.6183328307050564</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>415.2721732747317</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>6685000.237133035</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>124017.0673012482</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>1.0185515426929042</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>0.0185515426929042</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="24" t="str">
         <x:v>Medium bathydemersals (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
+      <x:c r="B9" s="31" t="n">
         <x:v>2.9850560805999997</x:v>
       </x:c>
+      <x:c r="C9" s="32" t="n">
+        <x:v>3.326068319189621</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="n">
+        <x:f>IF(C9="","",(1/'Metadata'!$B$5)^(C9-1))</x:f>
+        <x:v>211.86944024349154</x:v>
+      </x:c>
       <x:c r="E9" s="31" t="n">
-        <x:v>2.9850560805999997</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
-        <x:f>IF(E9=0,"",I9/E9)</x:f>
-        <x:v>235.62729355590892</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="n">
-        <x:f>IF(C9=0,"",SUMIF('Species'!$G$2:$G$87,A9,'Species'!$U$2:$U$87))</x:f>
-        <x:v>703.360685384387</x:v>
-      </x:c>
-      <x:c r="J9" s="32" t="n">
-        <x:v>3.326068319189621</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>IF(J9="","",(1/'Metadata'!$B$5)^(J9-1))</x:f>
-        <x:v>211.86944024349154</x:v>
-      </x:c>
-      <x:c r="L9" s="31" t="n">
-        <x:f>IF(E9=0,"",E9*K9)</x:f>
+        <x:f>IF(B9=0,"",B9*D9)</x:f>
         <x:v>632.4421608921527</x:v>
-      </x:c>
-      <x:c r="M9" s="31" t="n">
-        <x:f>IF(E9=0,"",I9-L9)</x:f>
-        <x:v>70.91852449223427</x:v>
-      </x:c>
-      <x:c r="N9" s="32" t="n">
-        <x:f>IF(L9=0,"",I9/L9)</x:f>
-        <x:v>1.1121344035511378</x:v>
-      </x:c>
-      <x:c r="O9" s="34" t="n">
-        <x:f>IF(L9=0,"",M9/L9)</x:f>
-        <x:v>0.11213440355113778</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="18" customHeight="1">
       <x:c r="A10" s="24" t="str">
         <x:v>Medium bathypelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B10" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C10" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D10" s="31" t="n">
+      <x:c r="B10" s="31" t="n">
         <x:v>132.8862026048</x:v>
       </x:c>
+      <x:c r="C10" s="32" t="n">
+        <x:v>3.65</x:v>
+      </x:c>
+      <x:c r="D10" s="32" t="n">
+        <x:f>IF(C10="","",(1/'Metadata'!$B$5)^(C10-1))</x:f>
+        <x:v>446.683592150963</x:v>
+      </x:c>
       <x:c r="E10" s="31" t="n">
-        <x:v>132.8862026048</x:v>
-      </x:c>
-      <x:c r="F10" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H10" s="32" t="n">
-        <x:f>IF(E10=0,"",I10/E10)</x:f>
-        <x:v>446.683592150963</x:v>
-      </x:c>
-      <x:c r="I10" s="31" t="n">
-        <x:f>IF(C10=0,"",SUMIF('Species'!$G$2:$G$87,A10,'Species'!$U$2:$U$87))</x:f>
+        <x:f>IF(B10=0,"",B10*D10)</x:f>
         <x:v>59358.08632681272</x:v>
-      </x:c>
-      <x:c r="J10" s="32" t="n">
-        <x:v>3.65</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:f>IF(J10="","",(1/'Metadata'!$B$5)^(J10-1))</x:f>
-        <x:v>446.683592150963</x:v>
-      </x:c>
-      <x:c r="L10" s="31" t="n">
-        <x:f>IF(E10=0,"",E10*K10)</x:f>
-        <x:v>59358.08632681272</x:v>
-      </x:c>
-      <x:c r="M10" s="31" t="n">
-        <x:f>IF(E10=0,"",I10-L10)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N10" s="32" t="n">
-        <x:f>IF(L10=0,"",I10/L10)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O10" s="34" t="n">
-        <x:f>IF(L10=0,"",M10/L10)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="18" customHeight="1">
       <x:c r="A11" s="24" t="str">
         <x:v>Medium benthopelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B11" s="33" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="C11" s="33" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="D11" s="31" t="n">
+      <x:c r="B11" s="31" t="n">
         <x:v>2105.3664512677</x:v>
       </x:c>
+      <x:c r="C11" s="32" t="n">
+        <x:v>3.939599359718026</x:v>
+      </x:c>
+      <x:c r="D11" s="32" t="n">
+        <x:f>IF(C11="","",(1/'Metadata'!$B$5)^(C11-1))</x:f>
+        <x:v>870.1604892701981</x:v>
+      </x:c>
       <x:c r="E11" s="31" t="n">
-        <x:v>2105.3664512677</x:v>
-      </x:c>
-      <x:c r="F11" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G11" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H11" s="32" t="n">
-        <x:f>IF(E11=0,"",I11/E11)</x:f>
-        <x:v>881.1291998112202</x:v>
-      </x:c>
-      <x:c r="I11" s="31" t="n">
-        <x:f>IF(C11=0,"",SUMIF('Species'!$G$2:$G$87,A11,'Species'!$U$2:$U$87))</x:f>
-        <x:v>1855099.856514897</x:v>
-      </x:c>
-      <x:c r="J11" s="32" t="n">
-        <x:v>3.939599359718026</x:v>
-      </x:c>
-      <x:c r="K11" s="32" t="n">
-        <x:f>IF(J11="","",(1/'Metadata'!$B$5)^(J11-1))</x:f>
-        <x:v>870.1604892701981</x:v>
-      </x:c>
-      <x:c r="L11" s="31" t="n">
-        <x:f>IF(E11=0,"",E11*K11)</x:f>
+        <x:f>IF(B11=0,"",B11*D11)</x:f>
         <x:v>1832006.7013281626</x:v>
-      </x:c>
-      <x:c r="M11" s="31" t="n">
-        <x:f>IF(E11=0,"",I11-L11)</x:f>
-        <x:v>23093.155186734395</x:v>
-      </x:c>
-      <x:c r="N11" s="32" t="n">
-        <x:f>IF(L11=0,"",I11/L11)</x:f>
-        <x:v>1.012605387944265</x:v>
-      </x:c>
-      <x:c r="O11" s="34" t="n">
-        <x:f>IF(L11=0,"",M11/L11)</x:f>
-        <x:v>0.012605387944264827</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="18" customHeight="1">
       <x:c r="A12" s="24" t="str">
         <x:v>Medium demersals (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B12" s="33" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="C12" s="33" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="D12" s="31" t="n">
+      <x:c r="B12" s="31" t="n">
         <x:v>72351.5873018483</x:v>
       </x:c>
+      <x:c r="C12" s="32" t="n">
+        <x:v>3.7662414289097095</x:v>
+      </x:c>
+      <x:c r="D12" s="32" t="n">
+        <x:f>IF(C12="","",(1/'Metadata'!$B$5)^(C12-1))</x:f>
+        <x:v>583.7695377663516</x:v>
+      </x:c>
       <x:c r="E12" s="31" t="n">
-        <x:v>72351.5873018483</x:v>
-      </x:c>
-      <x:c r="F12" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G12" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H12" s="32" t="n">
-        <x:f>IF(E12=0,"",I12/E12)</x:f>
-        <x:v>770.9272838380698</x:v>
-      </x:c>
-      <x:c r="I12" s="31" t="n">
-        <x:f>IF(C12=0,"",SUMIF('Species'!$G$2:$G$87,A12,'Species'!$U$2:$U$87))</x:f>
-        <x:v>55777812.67998689</x:v>
-      </x:c>
-      <x:c r="J12" s="32" t="n">
-        <x:v>3.7662414289097095</x:v>
-      </x:c>
-      <x:c r="K12" s="32" t="n">
-        <x:f>IF(J12="","",(1/'Metadata'!$B$5)^(J12-1))</x:f>
-        <x:v>583.7695377663516</x:v>
-      </x:c>
-      <x:c r="L12" s="31" t="n">
-        <x:f>IF(E12=0,"",E12*K12)</x:f>
+        <x:f>IF(B12=0,"",B12*D12)</x:f>
         <x:v>42236652.67586181</x:v>
-      </x:c>
-      <x:c r="M12" s="31" t="n">
-        <x:f>IF(E12=0,"",I12-L12)</x:f>
-        <x:v>13541160.004125074</x:v>
-      </x:c>
-      <x:c r="N12" s="32" t="n">
-        <x:f>IF(L12=0,"",I12/L12)</x:f>
-        <x:v>1.3206021108738057</x:v>
-      </x:c>
-      <x:c r="O12" s="34" t="n">
-        <x:f>IF(L12=0,"",M12/L12)</x:f>
-        <x:v>0.32060211087380575</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="18" customHeight="1">
       <x:c r="A13" s="24" t="str">
         <x:v>Medium pelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B13" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C13" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D13" s="31" t="n">
+      <x:c r="B13" s="31" t="n">
         <x:v>1089.3164204162</x:v>
       </x:c>
+      <x:c r="C13" s="32" t="n">
+        <x:v>3.3414689705853777</x:v>
+      </x:c>
+      <x:c r="D13" s="32" t="n">
+        <x:f>IF(C13="","",(1/'Metadata'!$B$5)^(C13-1))</x:f>
+        <x:v>219.5174103028186</x:v>
+      </x:c>
       <x:c r="E13" s="31" t="n">
-        <x:v>1089.3164204162</x:v>
-      </x:c>
-      <x:c r="F13" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G13" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H13" s="32" t="n">
-        <x:f>IF(E13=0,"",I13/E13)</x:f>
-        <x:v>223.9065364734337</x:v>
-      </x:c>
-      <x:c r="I13" s="31" t="n">
-        <x:f>IF(C13=0,"",SUMIF('Species'!$G$2:$G$87,A13,'Species'!$U$2:$U$87))</x:f>
-        <x:v>243905.0668190301</x:v>
-      </x:c>
-      <x:c r="J13" s="32" t="n">
-        <x:v>3.3414689705853777</x:v>
-      </x:c>
-      <x:c r="K13" s="32" t="n">
-        <x:f>IF(J13="","",(1/'Metadata'!$B$5)^(J13-1))</x:f>
-        <x:v>219.5174103028186</x:v>
-      </x:c>
-      <x:c r="L13" s="31" t="n">
-        <x:f>IF(E13=0,"",E13*K13)</x:f>
+        <x:f>IF(B13=0,"",B13*D13)</x:f>
         <x:v>239123.9196101006</x:v>
-      </x:c>
-      <x:c r="M13" s="31" t="n">
-        <x:f>IF(E13=0,"",I13-L13)</x:f>
-        <x:v>4781.147208929498</x:v>
-      </x:c>
-      <x:c r="N13" s="32" t="n">
-        <x:f>IF(L13=0,"",I13/L13)</x:f>
-        <x:v>1.0199944330819155</x:v>
-      </x:c>
-      <x:c r="O13" s="34" t="n">
-        <x:f>IF(L13=0,"",M13/L13)</x:f>
-        <x:v>0.0199944330819155</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="18" customHeight="1">
       <x:c r="A14" s="24" t="str">
         <x:v>Other demersal invertebrates</x:v>
       </x:c>
-      <x:c r="B14" s="33" t="n">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C14" s="33" t="n">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="D14" s="31" t="n">
+      <x:c r="B14" s="31" t="n">
         <x:v>307.98308599079996</x:v>
       </x:c>
+      <x:c r="C14" s="32" t="n">
+        <x:v>2.4908485252527823</x:v>
+      </x:c>
+      <x:c r="D14" s="32" t="n">
+        <x:f>IF(C14="","",(1/'Metadata'!$B$5)^(C14-1))</x:f>
+        <x:v>30.963391588667157</x:v>
+      </x:c>
       <x:c r="E14" s="31" t="n">
-        <x:v>307.98308599079996</x:v>
-      </x:c>
-      <x:c r="F14" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G14" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H14" s="32" t="n">
-        <x:f>IF(E14=0,"",I14/E14)</x:f>
-        <x:v>31.533087127908207</x:v>
-      </x:c>
-      <x:c r="I14" s="31" t="n">
-        <x:f>IF(C14=0,"",SUMIF('Species'!$G$2:$G$87,A14,'Species'!$U$2:$U$87))</x:f>
-        <x:v>9711.65748446994</x:v>
-      </x:c>
-      <x:c r="J14" s="32" t="n">
-        <x:v>2.4908485252527823</x:v>
-      </x:c>
-      <x:c r="K14" s="32" t="n">
-        <x:f>IF(J14="","",(1/'Metadata'!$B$5)^(J14-1))</x:f>
-        <x:v>30.963391588667157</x:v>
-      </x:c>
-      <x:c r="L14" s="31" t="n">
-        <x:f>IF(E14=0,"",E14*K14)</x:f>
+        <x:f>IF(B14=0,"",B14*D14)</x:f>
         <x:v>9536.20089421929</x:v>
-      </x:c>
-      <x:c r="M14" s="31" t="n">
-        <x:f>IF(E14=0,"",I14-L14)</x:f>
-        <x:v>175.45659025065106</x:v>
-      </x:c>
-      <x:c r="N14" s="32" t="n">
-        <x:f>IF(L14=0,"",I14/L14)</x:f>
-        <x:v>1.0183990031456878</x:v>
-      </x:c>
-      <x:c r="O14" s="34" t="n">
-        <x:f>IF(L14=0,"",M14/L14)</x:f>
-        <x:v>0.01839900314568775</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="18" customHeight="1">
       <x:c r="A15" s="24" t="str">
         <x:v>Shrimps</x:v>
       </x:c>
-      <x:c r="B15" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C15" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D15" s="31" t="n">
+      <x:c r="B15" s="31" t="n">
         <x:v>0.12551626440000002</x:v>
       </x:c>
+      <x:c r="C15" s="32" t="n">
+        <x:v>2.796593739058091</x:v>
+      </x:c>
+      <x:c r="D15" s="32" t="n">
+        <x:f>IF(C15="","",(1/'Metadata'!$B$5)^(C15-1))</x:f>
+        <x:v>62.602797256828204</x:v>
+      </x:c>
       <x:c r="E15" s="31" t="n">
-        <x:v>0.12551626440000002</x:v>
-      </x:c>
-      <x:c r="F15" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G15" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H15" s="32" t="n">
-        <x:f>IF(E15=0,"",I15/E15)</x:f>
-        <x:v>71.09531982622802</x:v>
-      </x:c>
-      <x:c r="I15" s="31" t="n">
-        <x:f>IF(C15=0,"",SUMIF('Species'!$G$2:$G$87,A15,'Species'!$U$2:$U$87))</x:f>
-        <x:v>8.9236189609114</x:v>
-      </x:c>
-      <x:c r="J15" s="32" t="n">
-        <x:v>2.796593739058091</x:v>
-      </x:c>
-      <x:c r="K15" s="32" t="n">
-        <x:f>IF(J15="","",(1/'Metadata'!$B$5)^(J15-1))</x:f>
-        <x:v>62.602797256828204</x:v>
-      </x:c>
-      <x:c r="L15" s="31" t="n">
-        <x:f>IF(E15=0,"",E15*K15)</x:f>
+        <x:f>IF(B15=0,"",B15*D15)</x:f>
         <x:v>7.857669252667645</x:v>
-      </x:c>
-      <x:c r="M15" s="31" t="n">
-        <x:f>IF(E15=0,"",I15-L15)</x:f>
-        <x:v>1.065949708243755</x:v>
-      </x:c>
-      <x:c r="N15" s="32" t="n">
-        <x:f>IF(L15=0,"",I15/L15)</x:f>
-        <x:v>1.1356572380393677</x:v>
-      </x:c>
-      <x:c r="O15" s="34" t="n">
-        <x:f>IF(L15=0,"",M15/L15)</x:f>
-        <x:v>0.1356572380393677</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="18" customHeight="1">
       <x:c r="A16" s="24" t="str">
         <x:v>Small pelagics (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B16" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C16" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D16" s="31" t="n">
+      <x:c r="B16" s="31" t="n">
         <x:v>157.89639890499998</x:v>
       </x:c>
+      <x:c r="C16" s="32" t="n">
+        <x:v>3.15</x:v>
+      </x:c>
+      <x:c r="D16" s="32" t="n">
+        <x:f>IF(C16="","",(1/'Metadata'!$B$5)^(C16-1))</x:f>
+        <x:v>141.2537544622754</x:v>
+      </x:c>
       <x:c r="E16" s="31" t="n">
-        <x:v>157.89639890499998</x:v>
-      </x:c>
-      <x:c r="F16" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G16" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H16" s="32" t="n">
-        <x:f>IF(E16=0,"",I16/E16)</x:f>
-        <x:v>141.2537544622754</x:v>
-      </x:c>
-      <x:c r="I16" s="31" t="n">
-        <x:f>IF(C16=0,"",SUMIF('Species'!$G$2:$G$87,A16,'Species'!$U$2:$U$87))</x:f>
+        <x:f>IF(B16=0,"",B16*D16)</x:f>
         <x:v>22303.459161404357</x:v>
-      </x:c>
-      <x:c r="J16" s="32" t="n">
-        <x:v>3.15</x:v>
-      </x:c>
-      <x:c r="K16" s="32" t="n">
-        <x:f>IF(J16="","",(1/'Metadata'!$B$5)^(J16-1))</x:f>
-        <x:v>141.2537544622754</x:v>
-      </x:c>
-      <x:c r="L16" s="31" t="n">
-        <x:f>IF(E16=0,"",E16*K16)</x:f>
-        <x:v>22303.459161404357</x:v>
-      </x:c>
-      <x:c r="M16" s="31" t="n">
-        <x:f>IF(E16=0,"",I16-L16)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N16" s="32" t="n">
-        <x:f>IF(L16=0,"",I16/L16)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O16" s="34" t="n">
-        <x:f>IF(L16=0,"",M16/L16)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="18" customHeight="1">
       <x:c r="A17" s="24" t="str">
         <x:v>Small to medium flatfishes (&lt;90 cm)</x:v>
       </x:c>
-      <x:c r="B17" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C17" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D17" s="31" t="n">
+      <x:c r="B17" s="31" t="n">
         <x:v>5270.0358891298</x:v>
       </x:c>
+      <x:c r="C17" s="32" t="n">
+        <x:v>3.975492494819844</x:v>
+      </x:c>
+      <x:c r="D17" s="32" t="n">
+        <x:f>IF(C17="","",(1/'Metadata'!$B$5)^(C17-1))</x:f>
+        <x:v>945.1320591738727</x:v>
+      </x:c>
       <x:c r="E17" s="31" t="n">
-        <x:v>5270.0358891298</x:v>
-      </x:c>
-      <x:c r="F17" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G17" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H17" s="32" t="n">
-        <x:f>IF(E17=0,"",I17/E17)</x:f>
-        <x:v>1324.7411293953471</x:v>
-      </x:c>
-      <x:c r="I17" s="31" t="n">
-        <x:f>IF(C17=0,"",SUMIF('Species'!$G$2:$G$87,A17,'Species'!$U$2:$U$87))</x:f>
-        <x:v>6981433.295719824</x:v>
-      </x:c>
-      <x:c r="J17" s="32" t="n">
-        <x:v>3.975492494819844</x:v>
-      </x:c>
-      <x:c r="K17" s="32" t="n">
-        <x:f>IF(J17="","",(1/'Metadata'!$B$5)^(J17-1))</x:f>
-        <x:v>945.1320591738727</x:v>
-      </x:c>
-      <x:c r="L17" s="31" t="n">
-        <x:f>IF(E17=0,"",E17*K17)</x:f>
+        <x:f>IF(B17=0,"",B17*D17)</x:f>
         <x:v>4980879.871813459</x:v>
-      </x:c>
-      <x:c r="M17" s="31" t="n">
-        <x:f>IF(E17=0,"",I17-L17)</x:f>
-        <x:v>2000553.4239063645</x:v>
-      </x:c>
-      <x:c r="N17" s="32" t="n">
-        <x:f>IF(L17=0,"",I17/L17)</x:f>
-        <x:v>1.4016465916448602</x:v>
-      </x:c>
-      <x:c r="O17" s="34" t="n">
-        <x:f>IF(L17=0,"",M17/L17)</x:f>
-        <x:v>0.4016465916448603</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="18" customHeight="1">
       <x:c r="A18" s="24" t="str">
         <x:v>Small to medium rays (&lt;90 cm)</x:v>
       </x:c>
-      <x:c r="B18" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C18" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D18" s="31" t="n">
+      <x:c r="B18" s="31" t="n">
         <x:v>385.2511992748</x:v>
       </x:c>
+      <x:c r="C18" s="32" t="n">
+        <x:v>3.7999999999999994</x:v>
+      </x:c>
+      <x:c r="D18" s="32" t="n">
+        <x:f>IF(C18="","",(1/'Metadata'!$B$5)^(C18-1))</x:f>
+        <x:v>630.9573444801923</x:v>
+      </x:c>
       <x:c r="E18" s="31" t="n">
-        <x:v>385.2511992748</x:v>
-      </x:c>
-      <x:c r="F18" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G18" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H18" s="32" t="n">
-        <x:f>IF(E18=0,"",I18/E18)</x:f>
-        <x:v>630.957344480193</x:v>
-      </x:c>
-      <x:c r="I18" s="31" t="n">
-        <x:f>IF(C18=0,"",SUMIF('Species'!$G$2:$G$87,A18,'Species'!$U$2:$U$87))</x:f>
-        <x:v>243077.07365223745</x:v>
-      </x:c>
-      <x:c r="J18" s="32" t="n">
-        <x:v>3.7999999999999994</x:v>
-      </x:c>
-      <x:c r="K18" s="32" t="n">
-        <x:f>IF(J18="","",(1/'Metadata'!$B$5)^(J18-1))</x:f>
-        <x:v>630.9573444801923</x:v>
-      </x:c>
-      <x:c r="L18" s="31" t="n">
-        <x:f>IF(E18=0,"",E18*K18)</x:f>
+        <x:f>IF(B18=0,"",B18*D18)</x:f>
         <x:v>243077.0736522372</x:v>
       </x:c>
-      <x:c r="M18" s="31" t="n">
-        <x:f>IF(E18=0,"",I18-L18)</x:f>
-        <x:v>2.6193447411060333e-10</x:v>
-      </x:c>
-      <x:c r="N18" s="32" t="n">
-        <x:f>IF(L18=0,"",I18/L18)</x:f>
-        <x:v>1.000000000000001</x:v>
-      </x:c>
-      <x:c r="O18" s="34" t="n">
-        <x:f>IF(L18=0,"",M18/L18)</x:f>
-        <x:v>1.0775778652220606e-15</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G18">
-    <x:cfRule type="cellIs" dxfId="2" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O18">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R117ae6ca30f745d7"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8f2abeb6eccc4398"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8269,7 +7170,7 @@
       <x:c r="B5" s="24" t="str">
         <x:v>catch_reconciled</x:v>
       </x:c>
-      <x:c r="C5" s="35" t="b">
+      <x:c r="C5" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D5" s="24" t="str">
@@ -8368,7 +7269,7 @@
         <x:v>commercial_ppr</x:v>
       </x:c>
       <x:c r="C12" s="24" t="n">
-        <x:v>256304293.92408934</x:v>
+        <x:v>248417328.29440054</x:v>
       </x:c>
       <x:c r="D12" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -8382,7 +7283,7 @@
         <x:v>functional_ppr</x:v>
       </x:c>
       <x:c r="C13" s="24" t="n">
-        <x:v>256304293.92408934</x:v>
+        <x:v>236031062.5418131</x:v>
       </x:c>
       <x:c r="D13" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -8396,7 +7297,7 @@
         <x:v>commercial_ppr_difference</x:v>
       </x:c>
       <x:c r="C14" s="24" t="n">
-        <x:v>0</x:v>
+        <x:v>-7886965.629688799</x:v>
       </x:c>
       <x:c r="D14" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -8410,7 +7311,7 @@
         <x:v>functional_ppr_difference</x:v>
       </x:c>
       <x:c r="C15" s="24" t="n">
-        <x:v>0</x:v>
+        <x:v>-20273231.382276237</x:v>
       </x:c>
       <x:c r="D15" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -8421,9 +7322,9 @@
         <x:v>EEZ_645</x:v>
       </x:c>
       <x:c r="B16" s="24" t="str">
-        <x:v>commercial_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C16" s="35" t="b">
+        <x:v>tl_coverage_complete</x:v>
+      </x:c>
+      <x:c r="C16" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D16" s="24" t="str">
@@ -8435,47 +7336,19 @@
         <x:v>EEZ_645</x:v>
       </x:c>
       <x:c r="B17" s="24" t="str">
-        <x:v>functional_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C17" s="35" t="b">
+        <x:v>group_ppr_within_convexity_bound</x:v>
+      </x:c>
+      <x:c r="C17" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D17" s="24" t="str">
         <x:v>boolean</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" ht="18" customHeight="1">
-      <x:c r="A18" s="24" t="str">
-        <x:v>EEZ_645</x:v>
-      </x:c>
-      <x:c r="B18" s="24" t="str">
-        <x:v>commercial_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C18" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D18" s="24" t="str">
-        <x:v>count</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" ht="18" customHeight="1">
-      <x:c r="A19" s="24" t="str">
-        <x:v>EEZ_645</x:v>
-      </x:c>
-      <x:c r="B19" s="24" t="str">
-        <x:v>functional_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C19" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D19" s="24" t="str">
-        <x:v>count</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rde04588749754170"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra62c09d5c8ff4cae"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8522,7 +7395,7 @@
       <x:c r="A5" s="22" t="str">
         <x:v>Transfer efficiency</x:v>
       </x:c>
-      <x:c r="B5" s="36" t="n">
+      <x:c r="B5" s="34" t="n">
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="C5" s="18" t="str">
